--- a/event_feedback_forms/038_event_crowd_management_feedback_form--event_feedback_forms.xlsx
+++ b/event_feedback_forms/038_event_crowd_management_feedback_form--event_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -769,8 +769,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -798,12 +798,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_poor',_'label':_'very_poor'}</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_poor', 'label': 'Very poor'}</t>
+          <t>Very poor</t>
         </is>
       </c>
     </row>
@@ -815,12 +815,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'poor',_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'poor', 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'average',_'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'average', 'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'good',_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'good', 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'excellent',_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'excellent', 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'very_dissatisfied',_'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'very_dissatisfied', 'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'dissatisfied',_'label':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'dissatisfied', 'label': 'Dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'neutral',_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'neutral', 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'satisfied',_'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'satisfied', 'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'very_satisfied',_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'very_satisfied', 'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
